--- a/kalshi_report.xlsx
+++ b/kalshi_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Log'!$A$1:$T$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Log'!$A$1:$T$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Trade Log'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Performance Analytics'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Equity Curve'!$1:$1</definedName>
@@ -52,10 +52,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
-      <color rgb="00C00000"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -79,14 +79,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFDCD4"/>
         <bgColor rgb="00FFDCD4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,12 +105,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00DEEAF1"/>
         <bgColor rgb="00DEEAF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,27 +132,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -273,12 +275,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity Curve'!$A$2:$A$26</f>
+              <f>'Equity Curve'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity Curve'!$C$2:$C$26</f>
+              <f>'Equity Curve'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +393,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity Curve'!$A$2:$A$26</f>
+              <f>'Equity Curve'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity Curve'!$G$2:$G$26</f>
+              <f>'Equity Curve'!$G$2:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -796,7 +798,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>$1,308.28</t>
+          <t>$1,086.15</t>
         </is>
       </c>
     </row>
@@ -820,7 +822,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>$308.28</t>
+          <t>$86.15</t>
         </is>
       </c>
     </row>
@@ -832,7 +834,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>$1,318.64</t>
+          <t>$1,128.93</t>
         </is>
       </c>
     </row>
@@ -856,7 +858,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -868,7 +870,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -886,7 +888,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -897,7 +899,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>17 / 7</t>
+          <t>9 / 11</t>
         </is>
       </c>
     </row>
@@ -909,7 +911,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -921,7 +923,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.28</t>
         </is>
       </c>
     </row>
@@ -933,7 +935,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>$27.22</t>
+          <t>$43.84</t>
         </is>
       </c>
     </row>
@@ -945,7 +947,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>$-23.38</t>
+          <t>$-28.03</t>
         </is>
       </c>
     </row>
@@ -957,7 +959,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.56</t>
         </is>
       </c>
     </row>
@@ -969,7 +971,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>$12.47</t>
+          <t>$4.31</t>
         </is>
       </c>
     </row>
@@ -981,7 +983,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>62.98</t>
+          <t>11.23</t>
         </is>
       </c>
     </row>
@@ -993,7 +995,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>422560124921173760.00</t>
+          <t>180289059324550496.00</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1014,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>$-38.92</t>
+          <t>$-33.76</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1026,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>$132.03</t>
+          <t>$206.21</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1037,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1045,7 +1047,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1097,7 +1099,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19 10:24:10</t>
+          <t>2026-06-27 03:10:28</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1111,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18 to 2026-03-18</t>
+          <t>2026-06-18 to 2026-06-19</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1122,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1131,7 +1133,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -1186,24 +1188,24 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>71.4%</t>
+        <v>9</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>10.315</v>
+        <v>96.51649999999998</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.473571428571429</v>
+        <v>5.677441176470587</v>
       </c>
     </row>
     <row r="41">
@@ -1213,24 +1215,24 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>85.7%</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>128.095</v>
+        <v>4.125</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>18.29928571428571</v>
+        <v>2.0625</v>
       </c>
     </row>
     <row r="42">
@@ -1240,24 +1242,24 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>47.31999999999999</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>23.66</v>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1267,24 +1269,24 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>122.555</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>30.63875</v>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>-14.49</v>
       </c>
     </row>
   </sheetData>
@@ -1300,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1326,182 +1328,182 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Trade #</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Time (ET)</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Contracts</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Gross PnL</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Net PnL</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Cumulative PnL</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Win/Loss</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Price to Beat</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>Exit Spot</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Edge at Entry</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>Window ID</t>
         </is>
       </c>
-      <c r="R1" s="6" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Time to Expiry</t>
         </is>
       </c>
-      <c r="S1" s="6" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Result Correct</t>
         </is>
       </c>
-      <c r="T1" s="6" t="inlineStr">
+      <c r="T1" s="8" t="inlineStr">
         <is>
           <t>Equity Trend</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>18:45:00</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>77.04000000000001</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>1075.97</v>
-      </c>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="F2" s="9" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>-29.84</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>-31.37</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>968.63</v>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>kalshi15m</t>
         </is>
       </c>
-      <c r="N2" s="7" t="n">
-        <v>2202.3175</v>
-      </c>
-      <c r="O2" s="7" t="n">
-        <v>2204.485</v>
-      </c>
-      <c r="P2" s="7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="Q2" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 17:45</t>
-        </is>
-      </c>
-      <c r="R2" s="7" t="n">
+      <c r="N2" s="9" t="n">
+        <v>62803.1</v>
+      </c>
+      <c r="O2" s="9" t="n">
+        <v>62781.2</v>
+      </c>
+      <c r="P2" s="9" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-18 22:30</t>
+        </is>
+      </c>
+      <c r="R2" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="S2" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr"/>
+      <c r="T2" s="9" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1509,45 +1511,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.185</v>
+        <v>0.505</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>162</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>132.03</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>130.41</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>1206.38</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>57</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>-28.79</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>-29.36</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>939.28</v>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1556,17 +1558,17 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.4572</v>
+        <v>62781.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4568</v>
+        <v>62848.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0.315</v>
+        <v>0.005</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-18 17:45</t>
+          <t>2026-06-18 22:45</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -1574,86 +1576,86 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>14:30:00</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>XRP</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>1221.98</v>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="F4" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>924.33</v>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>kalshi15m</t>
         </is>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>2215.265</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>2198.255</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 18:15</t>
-        </is>
-      </c>
-      <c r="R4" s="7" t="n">
+      <c r="N4" s="9" t="n">
+        <v>1.1481</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>1.1468</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-18 22:45</t>
+        </is>
+      </c>
+      <c r="R4" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T4" s="7" t="inlineStr"/>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1661,17 +1663,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1680,26 +1682,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.715</v>
+        <v>0.051</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>1235.73</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>539</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>-27.76</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>-33.15</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>891.1799999999999</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1708,17 +1710,17 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.4651</v>
+        <v>62919.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4596</v>
+        <v>62827.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0.215</v>
+        <v>0.449</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-03-18 18:15</t>
+          <t>2026-06-19 00:00</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1726,86 +1728,86 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>14:45:00</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7" t="n">
+      <c r="F6" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>-36.51</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>-37</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>1198.74</v>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="I6" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>912.99</v>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>kalshi15m</t>
         </is>
       </c>
-      <c r="N6" s="7" t="n">
-        <v>71680.95</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>71634.60000000001</v>
-      </c>
-      <c r="P6" s="7" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 18:30</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="n">
+      <c r="N6" s="9" t="n">
+        <v>62827.7</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>62927.55</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:15</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="T6" s="7" t="inlineStr"/>
+      <c r="T6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1813,45 +1815,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>20:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.74</v>
+        <v>0.055</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>1211.24</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>502</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>-27.61</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>-32.63</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>880.36</v>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1860,17 +1862,17 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.4596</v>
+        <v>62927.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.462</v>
+        <v>63023.775</v>
       </c>
       <c r="P7" t="n">
-        <v>0.24</v>
+        <v>0.445</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-03-18 18:30</t>
+          <t>2026-06-19 00:30</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1884,80 +1886,80 @@
       <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>233</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>206.21</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>203.88</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>1084.23</v>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>kalshi15m</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>62986.2</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>62939.4</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 01:00</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>1221.81</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>71634.60000000001</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>71103.05</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 18:45</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v>900</v>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr"/>
+      <c r="T8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1965,12 +1967,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>21:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1980,28 +1982,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.695</v>
+        <v>0.675</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>52</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>1237.15</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>1099.35</v>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2012,17 +2014,17 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>71103.05</v>
+        <v>62894.85</v>
       </c>
       <c r="O9" t="n">
-        <v>71343.2</v>
+        <v>62882.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00</t>
+          <t>2026-06-19 01:30</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -2036,80 +2038,80 @@
       <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>15:30:00</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>SOL</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>-33.22</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>-34.12</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>1065.23</v>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>kalshi15m</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>62882.6</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>62991.625</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 01:45</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>1255.35</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>89.80500000000001</v>
-      </c>
-      <c r="O10" s="7" t="n">
-        <v>89.855</v>
-      </c>
-      <c r="P10" s="7" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 19:15</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="n">
-        <v>900</v>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr"/>
+      <c r="T10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2117,43 +2119,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:30:01</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>65</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>-36.73</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>-37.38</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>1217.98</v>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>-16.41</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>1048.32</v>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -2164,17 +2166,17 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.4566</v>
+        <v>1708.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4541</v>
+        <v>1713.555</v>
       </c>
       <c r="P11" t="n">
-        <v>0.065</v>
+        <v>0.165</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-03-18 19:15</t>
+          <t>2026-06-19 01:45</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -2188,80 +2190,80 @@
       <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>22:15:00</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>236</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>-31.86</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-34.22</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>1014.1</v>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>kalshi15m</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>62991.625</v>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>62993.05</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:00</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>1230.47</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>71278.5</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>71063.95</v>
-      </c>
-      <c r="P12" s="7" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 19:30</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v>900</v>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr"/>
+      <c r="T12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2269,43 +2271,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>01:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.67</v>
+        <v>0.485</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>15.84</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>1245.83</v>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
+        <v>63</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>1045.92</v>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2316,17 +2318,17 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2193.6525</v>
+        <v>62580.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2191.615</v>
+        <v>62453.85</v>
       </c>
       <c r="P13" t="n">
-        <v>0.17</v>
+        <v>0.015</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-03-18 19:30</t>
+          <t>2026-06-19 04:45</t>
         </is>
       </c>
       <c r="R13" t="n">
@@ -2334,86 +2336,86 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>01:30:01</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="F14" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>1065.94</v>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>kalshi15m</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>62633.4</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>62580.1</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:15</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>32.55</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>31.85</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>1277.68</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>71063.95</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>71056.3</v>
-      </c>
-      <c r="P14" s="7" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 19:45</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="n">
-        <v>900</v>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr"/>
+      <c r="T14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2421,17 +2423,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>01:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2440,24 +2442,24 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.675</v>
+        <v>0.435</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>1295</v>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>1107.01</v>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2468,17 +2470,17 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2191.615</v>
+        <v>62580.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2185.7675</v>
+        <v>62620.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0.175</v>
+        <v>0.065</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-18 19:45</t>
+          <t>2026-06-19 05:30</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -2486,76 +2488,86 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>16:20:28</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="F16" s="9" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>-33.76</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>-35.33</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>1071.68</v>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>kalshi15m</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>62620.4</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>62704.45</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:45</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>1290.73</v>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr"/>
-      <c r="P16" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q16" s="7" t="inlineStr"/>
-      <c r="R16" s="7" t="inlineStr"/>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr"/>
+      <c r="T16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2563,12 +2575,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:20:28</t>
+          <t>02:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,28 +2590,28 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.6</v>
+        <v>0.255</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>1286.46</v>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
+        <v>128</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>-32.64</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-33.92</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>1037.76</v>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -2609,85 +2621,105 @@
           <t>kalshi15m</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>62704.45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>62809.6</v>
+      </c>
       <c r="P17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+        <v>0.245</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-06-19 06:00</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>900</v>
+      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>16:20:28</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>1282.19</v>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="F18" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>1057.78</v>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>kalshi15m</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr"/>
-      <c r="P18" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q18" s="7" t="inlineStr"/>
-      <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr"/>
+      <c r="N18" s="9" t="n">
+        <v>1691.565</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>1694.9225</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 07:45</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2695,12 +2727,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:20:28</t>
+          <t>06:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2710,126 +2742,136 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>66</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>-32.01</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>-32.67</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>1025.11</v>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>kalshi15m</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>62356.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>62506.175</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:00</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>900</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>06:30:00</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="G20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="n">
-        <v>7</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>1285.62</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="H20" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>1045.65</v>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>kalshi15m</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>16:30:00</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>144</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>-38.88</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>-40.32</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>1245.31</v>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>70809.64999999999</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>70992.35000000001</v>
-      </c>
-      <c r="P20" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 20:15</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="n">
+      <c r="N20" s="9" t="n">
+        <v>62506.175</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>62468</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:15</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="9" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="T20" s="7" t="inlineStr"/>
+      <c r="T20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2837,43 +2879,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:30:01</t>
+          <t>06:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.585</v>
+        <v>0.695</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>66</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>27.39</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>26.73</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>1272.04</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
+        <v>46</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>1059.22</v>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2884,17 +2926,17 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2171.4625</v>
+        <v>62468</v>
       </c>
       <c r="O21" t="n">
-        <v>2176.9325</v>
+        <v>62393.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-18 20:15</t>
+          <t>2026-06-19 10:30</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -2907,312 +2949,8 @@
       </c>
       <c r="T21" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>16:45:00</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>13.26</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>1284.78</v>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>70992.35000000001</v>
-      </c>
-      <c r="O22" s="7" t="n">
-        <v>71168.95</v>
-      </c>
-      <c r="P22" s="7" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 20:30</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="n">
-        <v>900</v>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>16:45:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>51</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="K23" s="8" t="n">
-        <v>1297.02</v>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>2176.9325</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2181.54</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-03-18 20:30</t>
-        </is>
-      </c>
-      <c r="R23" t="n">
-        <v>900</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>-38.92</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>-39.48</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>1257.54</v>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>2181.54</v>
-      </c>
-      <c r="O24" s="7" t="n">
-        <v>2187.755</v>
-      </c>
-      <c r="P24" s="7" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18 20:45</t>
-        </is>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v>900</v>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SOL</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>68</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>27.88</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>1285.42</v>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>kalshi15m</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>89.86499999999999</v>
-      </c>
-      <c r="O25" t="n">
-        <v>89.995</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-03-18 20:45</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
-        <v>900</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T25"/>
+  <autoFilter ref="A1:T21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3225,41 +2963,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Win Rate Analysis</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>vs Expected (50%)</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Z-score significance</t>
         </is>
@@ -3272,21 +3010,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.24</t>
         </is>
       </c>
     </row>
@@ -3297,21 +3035,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.7%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -3322,21 +3060,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+50.0%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -3347,53 +3085,53 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+25.0%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.00</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>PnL Distribution by Entry Price</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Total PnL</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Avg PnL</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
@@ -3406,17 +3144,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>132.03</v>
+        <v>89.14</v>
       </c>
       <c r="D11" t="n">
-        <v>132.03</v>
+        <v>17.83</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -3427,17 +3165,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>38.16</v>
+        <v>-97.3</v>
       </c>
       <c r="D12" t="n">
-        <v>19.08</v>
+        <v>-24.32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3448,17 +3186,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>8.59</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3469,17 +3207,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>36.05</v>
+        <v>-6.05</v>
       </c>
       <c r="D14" t="n">
-        <v>18.02</v>
+        <v>-1.51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3490,17 +3228,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>6.62</v>
+        <v>62.14</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1</v>
+        <v>20.71</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3511,17 +3249,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>86.31999999999999</v>
+        <v>29.63</v>
       </c>
       <c r="D16" t="n">
-        <v>6.64</v>
+        <v>14.81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3547,29 +3285,29 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Time of Day Analysis (ET hour)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Hour</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Avg PnL</t>
         </is>
@@ -3578,460 +3316,475 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35.99</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6.29</v>
+        <v>-29.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5.58</v>
+        <v>-21.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-11.02</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>2</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>-5.18</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>110.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-27.16</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Time to Expiry Analysis</t>
-        </is>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>31.6</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Win Rate</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Avg PnL</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Total PnL</t>
-        </is>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-33.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20.54</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Time to Expiry Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Avg PnL</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Total PnL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>0-60s</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-9.1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>60-180s</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B36" t="n">
         <v>0</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E36" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>180-450s</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B37" t="n">
         <v>0</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>450-900s</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B38" t="n">
         <v>0</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E38" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Rolling Win Rate</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>Trade #</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>5-trade rolling WR</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>10-trade rolling WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>3</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4040,13 +3793,13 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4055,43 +3808,43 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4100,47 +3853,47 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4149,41 +3902,44 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Asset Correlation (win/loss overlap)</t>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>20</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
+          <t>Asset Correlation (win/loss overlap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
           <t>Pair</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>Correlation</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BTC/ETH</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BTC/SOL</t>
+          <t>BTC/ETH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4195,7 +3951,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BTC/XRP</t>
+          <t>BTC/SOL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4207,7 +3963,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ETH/SOL</t>
+          <t>BTC/XRP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4219,7 +3975,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ETH/XRP</t>
+          <t>ETH/SOL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4231,89 +3987,101 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>ETH/XRP</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>SOL/XRP</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>Side Analysis</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="D75" s="11" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Avg PnL</t>
         </is>
       </c>
-      <c r="E75" s="11" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>Total PnL</t>
         </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>22</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>77.3%</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="E76" t="n">
-        <v>376.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>6</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E77" t="n">
+        <v>12.56</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>2</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>-38.9</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-77.8</v>
+      <c r="B78" t="n">
+        <v>14</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E78" t="n">
+        <v>73.59</v>
       </c>
     </row>
   </sheetData>
@@ -4329,41 +4097,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Trade #</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Cumulative PnL</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Peak</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Drawdown $</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Drawdown %</t>
         </is>
@@ -4402,24 +4170,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1077.04</v>
+        <v>970.16</v>
       </c>
       <c r="D3" t="n">
-        <v>77.04000000000001</v>
+        <v>-29.84</v>
       </c>
       <c r="E3" t="n">
-        <v>1077.04</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>29.84</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
@@ -4429,24 +4197,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1209.07</v>
+        <v>941.38</v>
       </c>
       <c r="D4" t="n">
-        <v>209.07</v>
+        <v>-58.62</v>
       </c>
       <c r="E4" t="n">
-        <v>1209.07</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>58.62</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -4456,24 +4224,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1225.19</v>
+        <v>926.89</v>
       </c>
       <c r="D5" t="n">
-        <v>225.19</v>
+        <v>-73.11</v>
       </c>
       <c r="E5" t="n">
-        <v>1225.19</v>
+        <v>1000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>73.11</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
@@ -4483,24 +4251,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1239.44</v>
+        <v>899.13</v>
       </c>
       <c r="D6" t="n">
-        <v>239.44</v>
+        <v>-100.87</v>
       </c>
       <c r="E6" t="n">
-        <v>1239.44</v>
+        <v>1000</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>100.87</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-10.1%</t>
         </is>
       </c>
     </row>
@@ -4510,24 +4278,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1202.93</v>
+        <v>921.4299999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>202.93</v>
+        <v>-78.56999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1239.44</v>
+        <v>1000</v>
       </c>
       <c r="F7" t="n">
-        <v>36.51</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-7.9%</t>
         </is>
       </c>
     </row>
@@ -4537,24 +4305,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1215.93</v>
+        <v>893.8200000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>215.93</v>
+        <v>-106.18</v>
       </c>
       <c r="E8" t="n">
-        <v>1239.44</v>
-      </c>
-      <c r="F8" t="n">
-        <v>23.51</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
+        <v>1000</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>106.18</v>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>-10.6%</t>
         </is>
       </c>
     </row>
@@ -4564,24 +4332,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1226.98</v>
+        <v>1100.02</v>
       </c>
       <c r="D9" t="n">
-        <v>226.98</v>
+        <v>100.02</v>
       </c>
       <c r="E9" t="n">
-        <v>1239.44</v>
+        <v>1100.02</v>
       </c>
       <c r="F9" t="n">
-        <v>12.46</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4359,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1242.84</v>
+        <v>1115.62</v>
       </c>
       <c r="D10" t="n">
-        <v>242.84</v>
+        <v>115.62</v>
       </c>
       <c r="E10" t="n">
-        <v>1242.84</v>
+        <v>1115.62</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -4618,24 +4386,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1261.6</v>
+        <v>1082.41</v>
       </c>
       <c r="D11" t="n">
-        <v>261.6</v>
+        <v>82.41</v>
       </c>
       <c r="E11" t="n">
-        <v>1261.6</v>
+        <v>1115.62</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>33.21</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
@@ -4645,24 +4413,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1224.87</v>
+        <v>1065.99</v>
       </c>
       <c r="D12" t="n">
-        <v>224.87</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1261.6</v>
+        <v>1115.62</v>
       </c>
       <c r="F12" t="n">
-        <v>36.72</v>
+        <v>49.63</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
     </row>
@@ -4672,24 +4440,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1237.86</v>
+        <v>1034.13</v>
       </c>
       <c r="D13" t="n">
-        <v>237.86</v>
+        <v>34.13</v>
       </c>
       <c r="E13" t="n">
-        <v>1261.6</v>
+        <v>1115.62</v>
       </c>
       <c r="F13" t="n">
-        <v>23.74</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
@@ -4699,24 +4467,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1253.7</v>
+        <v>1066.58</v>
       </c>
       <c r="D14" t="n">
-        <v>253.7</v>
+        <v>66.58</v>
       </c>
       <c r="E14" t="n">
-        <v>1261.6</v>
+        <v>1115.62</v>
       </c>
       <c r="F14" t="n">
-        <v>7.9</v>
+        <v>49.04</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
     </row>
@@ -4726,24 +4494,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1286.25</v>
+        <v>1087.12</v>
       </c>
       <c r="D15" t="n">
-        <v>286.25</v>
+        <v>87.12</v>
       </c>
       <c r="E15" t="n">
-        <v>1286.25</v>
+        <v>1115.62</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>28.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
@@ -4753,17 +4521,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1304.12</v>
+        <v>1128.93</v>
       </c>
       <c r="D16" t="n">
-        <v>304.12</v>
+        <v>128.93</v>
       </c>
       <c r="E16" t="n">
-        <v>1304.12</v>
+        <v>1128.93</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -4780,24 +4548,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1299.92</v>
+        <v>1095.17</v>
       </c>
       <c r="D17" t="n">
-        <v>299.92</v>
+        <v>95.17</v>
       </c>
       <c r="E17" t="n">
-        <v>1304.12</v>
+        <v>1128.93</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2</v>
+        <v>33.76</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
@@ -4807,24 +4575,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1295.72</v>
+        <v>1062.53</v>
       </c>
       <c r="D18" t="n">
-        <v>295.72</v>
+        <v>62.53</v>
       </c>
       <c r="E18" t="n">
-        <v>1304.12</v>
+        <v>1128.93</v>
       </c>
       <c r="F18" t="n">
-        <v>8.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -4834,24 +4602,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1291.52</v>
+        <v>1083.07</v>
       </c>
       <c r="D19" t="n">
-        <v>291.52</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1304.12</v>
+        <v>1128.93</v>
       </c>
       <c r="F19" t="n">
-        <v>12.6</v>
+        <v>45.86</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
     </row>
@@ -4861,24 +4629,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1295.02</v>
+        <v>1051.06</v>
       </c>
       <c r="D20" t="n">
-        <v>295.02</v>
+        <v>51.06</v>
       </c>
       <c r="E20" t="n">
-        <v>1304.12</v>
+        <v>1128.93</v>
       </c>
       <c r="F20" t="n">
-        <v>9.1</v>
+        <v>77.87</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-6.9%</t>
         </is>
       </c>
     </row>
@@ -4888,24 +4656,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1256.14</v>
+        <v>1072.12</v>
       </c>
       <c r="D21" t="n">
-        <v>256.14</v>
+        <v>72.12</v>
       </c>
       <c r="E21" t="n">
-        <v>1304.12</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>47.98</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>-3.7%</t>
+        <v>1128.93</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.0%</t>
         </is>
       </c>
     </row>
@@ -4915,168 +4683,60 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1283.53</v>
+        <v>1086.15</v>
       </c>
       <c r="D22" t="n">
-        <v>283.53</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1304.12</v>
+        <v>1128.93</v>
       </c>
       <c r="F22" t="n">
-        <v>20.59</v>
+        <v>42.78</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1296.79</v>
-      </c>
-      <c r="D23" t="n">
-        <v>296.79</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1304.12</v>
-      </c>
-      <c r="F23" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1309.54</v>
-      </c>
-      <c r="D24" t="n">
-        <v>309.54</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1309.54</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-0.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Calmar Ratio</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1270.62</v>
-      </c>
-      <c r="D25" t="n">
-        <v>270.62</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1309.54</v>
-      </c>
-      <c r="F25" t="n">
-        <v>38.92</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-3.0%</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1299.18</v>
-      </c>
-      <c r="D26" t="n">
-        <v>299.18</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1309.54</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Calmar Ratio</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>6.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+          <t>0.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Ulcer Index</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1.46%</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5.47%</t>
         </is>
       </c>
     </row>
@@ -5094,187 +4754,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Day of Week</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Trades</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Day PnL</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Cumulative PnL</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Best Trade</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Worst Trade</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Assets Traded</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="n">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>70.8%</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>299.19</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>299.19</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>132.03</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>-38.92</v>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>BTC, ETH, SOL, XRP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="D2" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>206.21</v>
+      </c>
+      <c r="K2" s="9" t="n">
+        <v>-33.22</v>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>BTC, ETH, XRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-33.76</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>BTC, ETH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>70.8%</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>299.19</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>299.19</v>
-      </c>
-      <c r="J4" s="14" t="inlineStr"/>
-      <c r="K4" s="14" t="inlineStr"/>
-      <c r="L4" s="14" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Avg trades/day</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
+      <c r="B5" s="16" t="inlineStr"/>
+      <c r="C5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="16" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Avg win rate</t>
+          <t>Avg trades/day</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Avg win rate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Avg day PnL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>$299.19</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>$43.08</t>
         </is>
       </c>
     </row>
@@ -5291,78 +4997,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>WAIT Reason</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>% of Total</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>mispricing_weak</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>vol_too_high</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2912</v>
+        <v>4468</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>structural_model_invalid</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>spot_confidence_low</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2402</v>
+        <v>1807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>spot_confidence_low</t>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>lag_absent</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1671</v>
+        <v>1187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5370,95 +5076,95 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>lag_absent</t>
+          <t>structural_model_invalid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>828</v>
+        <v>964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>window_boundary</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>443</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>mispricing_weak</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>lag_confidence_low</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>297</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>uncertain_near_50</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>158</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>698</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>7.0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>window_boundary</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>477</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>lag_confidence_low</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>p_real_near_50</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>286</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>uncertain_near_50</t>
-        </is>
-      </c>
       <c r="B10" t="n">
-        <v>189</v>
+        <v>121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -5466,15 +5172,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sharpe</t>
+          <t>p_real_near_50</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -5482,189 +5188,221 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time_remaining_low</t>
+          <t>sharpe</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>alpha_edge_insufficient</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>venue_dislocation</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Interpretation Guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>structural_model_invalid — Structural probability model could not compute a valid p_base. Often indicates feed instability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>spot_confidence_low — Fewer than 2 price venues available. Feed unreliable.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lag_absent — Kalshi lag tracker has insufficient data to detect edge.</t>
+          <t>structural_model_invalid — Structural probability model could not compute a valid p_base. Often indicates feed instability.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mispricing_weak — Market price too close to model price; no edge.</t>
+          <t>spot_confidence_low — Fewer than 2 price venues available. Feed unreliable.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>position_open — Already holding a position for this asset/window.</t>
+          <t>lag_absent — Kalshi lag tracker has insufficient data to detect edge.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>window_boundary — Outside trading window (skip open/close).</t>
+          <t>mispricing_weak — Market price too close to model price; no edge.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>position_open — Already holding a position for this asset/window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_boundary — Outside trading window (skip open/close).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>portfolio_cap — Total exposure would exceed limit.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Per-Asset Top WAIT Reasons</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Top Reason</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>2nd Reason</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>3rd Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mispricing_weak</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>structural_model_invalid</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>edge</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>structural_model_invalid</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>mispricing_weak</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>spot_confidence_low</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>lag_absent</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>structural_model_invalid</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>mispricing_weak</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>spot_confidence_low</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>structural_model_invalid</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>vol_too_high</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>spot_confidence_low</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>lag_absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>vol_too_high</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>spot_confidence_low</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>window_boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>XRP</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>mispricing_weak</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>vol_too_high</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>spot_confidence_low</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>structural_model_invalid</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>window_boundary</t>
         </is>
       </c>
     </row>
@@ -5681,41 +5419,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Position Sizing Analysis</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Trade #</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Contracts</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Position Size ($)</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>% of Balance</t>
         </is>
@@ -5726,13 +5464,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="C3" t="n">
-        <v>0.28</v>
+        <v>0.195</v>
       </c>
       <c r="D3" t="n">
-        <v>29.96</v>
+        <v>29.84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -5745,17 +5483,17 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>0.185</v>
+        <v>0.505</v>
       </c>
       <c r="D4" t="n">
-        <v>29.97</v>
+        <v>28.79</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -5764,17 +5502,17 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="D5" t="n">
-        <v>35.88</v>
+        <v>14.49</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -5783,17 +5521,17 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>539</v>
       </c>
       <c r="C6" t="n">
-        <v>0.715</v>
+        <v>0.051</v>
       </c>
       <c r="D6" t="n">
-        <v>35.75</v>
+        <v>27.76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -5805,14 +5543,14 @@
         <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>0.745</v>
+        <v>0.545</v>
       </c>
       <c r="D7" t="n">
-        <v>36.51</v>
+        <v>26.71</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -5821,17 +5559,17 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>502</v>
       </c>
       <c r="C8" t="n">
-        <v>0.74</v>
+        <v>0.055</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>27.61</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -5840,13 +5578,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>233</v>
       </c>
       <c r="C9" t="n">
-        <v>0.765</v>
+        <v>0.115</v>
       </c>
       <c r="D9" t="n">
-        <v>35.95</v>
+        <v>26.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5859,13 +5597,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>0.695</v>
+        <v>0.675</v>
       </c>
       <c r="D10" t="n">
-        <v>36.14</v>
+        <v>32.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5878,13 +5616,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="C11" t="n">
-        <v>0.665</v>
+        <v>0.365</v>
       </c>
       <c r="D11" t="n">
-        <v>37.24</v>
+        <v>33.21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5897,17 +5635,17 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="D12" t="n">
-        <v>36.72</v>
+        <v>16.42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -5916,17 +5654,17 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>236</v>
       </c>
       <c r="C13" t="n">
-        <v>0.735</v>
+        <v>0.135</v>
       </c>
       <c r="D13" t="n">
-        <v>36.02</v>
+        <v>31.86</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -5935,17 +5673,17 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C14" t="n">
-        <v>0.67</v>
+        <v>0.485</v>
       </c>
       <c r="D14" t="n">
-        <v>32.16</v>
+        <v>30.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -5954,17 +5692,17 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C15" t="n">
-        <v>0.535</v>
+        <v>0.605</v>
       </c>
       <c r="D15" t="n">
-        <v>37.45</v>
+        <v>31.46</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -5973,17 +5711,17 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C16" t="n">
-        <v>0.675</v>
+        <v>0.435</v>
       </c>
       <c r="D16" t="n">
-        <v>37.12</v>
+        <v>32.19</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -5992,17 +5730,17 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6</v>
+        <v>0.215</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2</v>
+        <v>33.76</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -6011,17 +5749,17 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6</v>
+        <v>0.255</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2</v>
+        <v>32.64</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -6030,17 +5768,17 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2</v>
+        <v>31.46</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -6049,17 +5787,17 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="D20" t="n">
-        <v>3.5</v>
+        <v>32.01</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -6068,17 +5806,17 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="C21" t="n">
-        <v>0.27</v>
+        <v>0.595</v>
       </c>
       <c r="D21" t="n">
-        <v>38.88</v>
+        <v>30.94</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -6087,408 +5825,332 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C22" t="n">
-        <v>0.585</v>
+        <v>0.695</v>
       </c>
       <c r="D22" t="n">
-        <v>38.61</v>
+        <v>31.97</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="n">
-        <v>52</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="D23" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
           <t>3.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="n">
-        <v>51</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D24" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2.9%</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Avg position size</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$29.14</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="n">
-        <v>56</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="D25" t="n">
-        <v>38.92</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Max position size</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>$33.76</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="n">
-        <v>68</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="D26" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Avg position size</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>$30.95</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>% trades over 5%</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Max position size</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>$39.44</t>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Consecutive Loss Streaks</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>% trades over 5%</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Streak #</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Total Loss</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Recovery Trades</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Recovery PnL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>-100.87</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-27.61</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>206.21</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Consecutive Loss Streaks</t>
-        </is>
+      <c r="A33" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>-81.48999999999999</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>32.45</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Streak #</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Total Loss</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>Recovery Trades</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>Recovery PnL</t>
-        </is>
+      <c r="A34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-66.40000000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20.54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-36.51</v>
+        <v>-32.01</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+        <v>21.06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Drawdown Periods</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>Period #</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Trough</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Max DD ($)</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Max DD (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>1</v>
       </c>
-      <c r="D36" t="n">
-        <v>-36.73</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>12.98</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>-12.6</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>4</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-38.88</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>27.39</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>5</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-38.92</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>28.56</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Drawdown Periods</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Trough</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="n">
+        <v>106.18</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>Period #</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>Trough</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>Max DD ($)</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>Max DD (%)</t>
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>Stress Test (HYPOTHETICAL)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>1</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Win rate 45%: Expected PnL per trade</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Trough</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>24</v>
-      </c>
-      <c r="F45" t="n">
-        <v>47.98</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>3.7%</t>
+          <t>$4.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Win rate 45%: Projected balance after same # trades</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>$1086.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Avg loss +20%: Expected PnL per trade</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>$1.22</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>Stress Test (HYPOTHETICAL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Win rate 45%: Expected PnL per trade</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>$-0.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Win rate 45%: Projected balance after same # trades</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>$985.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Avg loss +20%: Expected PnL per trade</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>$11.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>3 concurrent max losses impact</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>$116.76</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>$101.27</t>
         </is>
       </c>
     </row>
